--- a/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://esqlabs.sharepoint.com/sites/Services/Freigegebene Dokumente/_Project_template_V02.00/WP1_V00.01/Parameters/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR.worktrees\update-aciclovir-pkml\inst\extdata\examples\TestProject\Configurations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="13_ncr:1_{74401FE8-0DB7-4671-9034-D4AD97DAF165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE66B4D0-8183-45FE-8047-14DAA08B635C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880F1CD1-70BF-4F87-A887-E5413A05C154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9020" yWindow="9480" windowWidth="28800" windowHeight="15290" tabRatio="965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="870" windowWidth="27640" windowHeight="19270" tabRatio="965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aciclovir_iv_250mg" sheetId="14" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>mg</t>
   </si>
   <si>
-    <t>Applications|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
+    <t>Events|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
   </si>
 </sst>
 </file>
@@ -104,9 +104,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -388,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC36B16-DE46-4C6E-A6ED-9C66C3DB41B7}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="89.81640625" bestFit="1" customWidth="1"/>
@@ -424,24 +423,6 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C7" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -687,15 +668,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="398d2b5b-77f8-4c5f-a794-3d35ce849315">
@@ -704,6 +676,15 @@
     <TaxCatchAll xmlns="1c52e43a-7a2d-43c4-9ede-f251c929c0a1" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -726,14 +707,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{253E2BCE-BEE3-46CA-82C7-E211846F5250}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D118C015-E179-46FB-B6E8-2D926D65EB7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -742,4 +715,12 @@
     <ds:schemaRef ds:uri="1c52e43a-7a2d-43c4-9ede-f251c929c0a1"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{253E2BCE-BEE3-46CA-82C7-E211846F5250}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Applications|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
+          <t>Events|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
+++ b/inst/extdata/examples/TestProject/Configurations/Applications.xlsx
@@ -1,28 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RudolfEngelke\Documents\RStudio.wd\esqlabsR.worktrees\pi-workflow\inst\extdata\examples\TestProject\Configurations\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FB32BF-B241-40FB-8B38-44C19CC994C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7790" yWindow="760" windowWidth="27640" windowHeight="19270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7790" yWindow="760" windowWidth="27640" windowHeight="19270" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Aciclovir_iv_250mg" sheetId="1" r:id="rId1"/>
-    <sheet name="Protocol_250mg" sheetId="2" r:id="rId2"/>
-    <sheet name="Protocol_500mg" sheetId="3" r:id="rId3"/>
+    <sheet name="Aciclovir_iv_250mg" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Protocol_250mg" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Protocol_500mg" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Container Path</t>
   </si>
@@ -43,22 +36,18 @@
   </si>
   <si>
     <t>Events|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Events|IV 250mg 10min|No formulation|Application_1|ProtocolSchemaItem</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -71,6 +60,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -90,22 +85,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="1" xr:uid="{50F91E0E-941E-40F8-8246-13206B329C82}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -406,14 +397,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="56.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.54296875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -427,14 +418,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>250</v>
       </c>
       <c r="D2" t="s">
@@ -443,18 +434,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="56.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.54296875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,14 +460,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>250</v>
       </c>
       <c r="D2" t="s">
@@ -484,18 +476,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="51.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7265625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,14 +502,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>500</v>
       </c>
       <c r="D2" t="s">
@@ -525,5 +518,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>